--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105350_W1.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105350_W1.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6072</v>
+        <v>2.5196</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7606</v>
+        <v>3.708</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1534</v>
+        <v>-1.1883</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9223</v>
+        <v>2.8465</v>
       </c>
       <c r="H2" t="n">
-        <v>1.363</v>
+        <v>1.3106</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5592</v>
+        <v>1.536</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7341</v>
+        <v>3.7523</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3709</v>
+        <v>1.3811</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3632</v>
+        <v>2.3712</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8118</v>
+        <v>-0.9058</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0078</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.8353</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6081</v>
+        <v>0.6076</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0265</v>
+        <v>-0.0443</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5816</v>
+        <v>0.652</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2116</v>
+        <v>1.1835</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5255</v>
+        <v>-0.4984</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7371</v>
+        <v>1.6819</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1825</v>
+        <v>-2.142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1484</v>
+        <v>0.1182</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3309</v>
+        <v>-2.2602</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.5698</v>
+        <v>-1.4275</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3265</v>
+        <v>0.368</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.8963</v>
+        <v>-1.7955</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6128</v>
+        <v>-0.7146</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1781</v>
+        <v>-0.2498</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4347</v>
+        <v>-0.4648</v>
       </c>
       <c r="P3" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2465</v>
+        <v>0.1786</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0518</v>
+        <v>-0.0743</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1946</v>
+        <v>0.253</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3016</v>
+        <v>1.3109</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0785</v>
+        <v>0.078</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.458</v>
+        <v>0.3237</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2094</v>
+        <v>0.1116</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2486</v>
+        <v>0.2121</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2381</v>
+        <v>-0.2814</v>
       </c>
       <c r="H4" t="n">
-        <v>0.455</v>
+        <v>0.4427</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6931</v>
+        <v>-0.7241</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9111</v>
+        <v>0.9566</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8004</v>
+        <v>0.8454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1108</v>
+        <v>0.1112</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1493</v>
+        <v>-1.238</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3454</v>
+        <v>-0.4027</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.8353</v>
       </c>
       <c r="P4" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3075</v>
+        <v>2.295</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.6911</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6828</v>
+        <v>0.532</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1591</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.004</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.004</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5158</v>
+        <v>-0.4572</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7448</v>
+        <v>0.8383</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2606</v>
+        <v>-1.2955</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.9547</v>
+        <v>-3.8833</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5735</v>
+        <v>-0.5621</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.3812</v>
+        <v>-3.3212</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3264</v>
+        <v>-1.1457</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0579</v>
+        <v>0.0199</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2685</v>
+        <v>-1.1656</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6282</v>
+        <v>-2.7376</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.582</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1126</v>
+        <v>-2.1556</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4074</v>
+        <v>-0.4264</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6212</v>
+        <v>-0.7211</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2138</v>
+        <v>0.2947</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6925</v>
+        <v>2.705</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6925</v>
+        <v>2.705</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5613</v>
+        <v>-0.6551</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6534</v>
+        <v>-0.7098</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0921</v>
+        <v>0.0547</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.575</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7447</v>
+        <v>-0.7502</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1888</v>
+        <v>0.1752</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.149</v>
+        <v>-0.1133</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7398</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5908</v>
+        <v>0.5928</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4069</v>
+        <v>-0.4617</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0049</v>
+        <v>-0.0441</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.402</v>
+        <v>-0.4176</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6238</v>
+        <v>0.5568</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5109</v>
+        <v>0.4134</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1129</v>
+        <v>0.1434</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7831</v>
+        <v>-1.7843</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7846</v>
+        <v>-0.7803</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.004</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.44</v>
+        <v>-1.3618</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8456</v>
+        <v>-2.7356</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4056</v>
+        <v>1.3738</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.3458</v>
+        <v>-5.2407</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8249</v>
+        <v>-1.815</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.5209</v>
+        <v>-3.4257</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.4522</v>
+        <v>-3.2088</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3054</v>
+        <v>-1.1977</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1468</v>
+        <v>-2.0111</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8937</v>
+        <v>-2.0319</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5195</v>
+        <v>-0.6173</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3742</v>
+        <v>-1.4146</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5383</v>
+        <v>-2.5244</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3075</v>
+        <v>2.295</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0733</v>
+        <v>1.0236</v>
       </c>
       <c r="T7" t="n">
-        <v>0.16</v>
+        <v>-0.0091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9133</v>
+        <v>1.0327</v>
       </c>
       <c r="V7" t="n">
-        <v>3.0633</v>
+        <v>3.0848</v>
       </c>
       <c r="W7" t="n">
-        <v>2.9849</v>
+        <v>3.0068</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0785</v>
+        <v>0.078</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6792</v>
+        <v>-2.6875</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5575</v>
+        <v>-2.5662</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1217</v>
+        <v>-0.1213</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5712</v>
+        <v>-0.5881</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5702</v>
+        <v>-0.5793</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,31 +1095,31 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5712</v>
+        <v>-0.5881</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5702</v>
+        <v>-0.5793</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0768</v>
+        <v>-2.0655</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0312</v>
+        <v>-0.0339</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.25</v>
+        <v>-0.2712</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2187</v>
+        <v>0.2373</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3924</v>
+        <v>-3.379</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0087</v>
+        <v>-3.9061</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3836</v>
+        <v>0.527</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4393</v>
+        <v>-3.3078</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7964</v>
+        <v>-0.9295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3571</v>
+        <v>-2.3782</v>
       </c>
       <c r="J9" t="n">
-        <v>0.908</v>
+        <v>-1.5257</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7906</v>
+        <v>-0.4475</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6985</v>
+        <v>-1.0782</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3473</v>
+        <v>-1.7821</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0059</v>
+        <v>-0.482</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3414</v>
+        <v>-1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1538</v>
+        <v>0.2295</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3075</v>
+        <v>-1.377</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1538</v>
+        <v>1.6065</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.1395</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6862</v>
+        <v>-0.7641</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0361</v>
+        <v>0.6246</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.077</v>
+        <v>-0.1612</v>
       </c>
       <c r="W9" t="n">
-        <v>1.077</v>
+        <v>-0.2393</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.154</v>
+        <v>0.078</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.462</v>
+        <v>-3.4395</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0615</v>
+        <v>-1.0261</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5996</v>
+        <v>-2.4134</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4062</v>
+        <v>-0.4733</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9149</v>
+        <v>-0.8102</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4913</v>
+        <v>0.3369</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8134</v>
+        <v>0.947</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5607</v>
+        <v>-0.7573</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2527</v>
+        <v>1.7043</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5928</v>
+        <v>-1.4203</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3542</v>
+        <v>-0.0529</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2386</v>
+        <v>-1.3675</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2308</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3845</v>
+        <v>-2.295</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6153</v>
+        <v>1.1475</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.119</v>
+        <v>-0.7367</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6176</v>
+        <v>-0.7602</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4986</v>
+        <v>0.0235</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1676</v>
+        <v>-1.082</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2461</v>
+        <v>1.082</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0785</v>
+        <v>-2.164</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.692</v>
+        <v>-3.6593</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7831</v>
+        <v>-3.7224</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0911</v>
+        <v>0.0631</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7577</v>
+        <v>-3.6863</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2137</v>
+        <v>-1.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5441</v>
+        <v>-2.5027</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.9499</v>
+        <v>-2.8157</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.378</v>
+        <v>-1.31</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5719</v>
+        <v>-1.5057</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8078</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1643</v>
+        <v>0.1264</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9722</v>
+        <v>-0.9969</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R11" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1503</v>
+        <v>0.1056</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1744</v>
+        <v>0.09</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0241</v>
+        <v>0.0156</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0169</v>
+        <v>-4.9806</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4519</v>
+        <v>-2.3471</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.565</v>
+        <v>-2.6335</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8586</v>
+        <v>-2.7868</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7962</v>
+        <v>-1.6922</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0624</v>
+        <v>-1.0946</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6756</v>
+        <v>-1.4929</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7864</v>
+        <v>-1.604</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1108</v>
+        <v>0.1112</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.183</v>
+        <v>-1.2939</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0098</v>
+        <v>-0.0881</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1732</v>
+        <v>-1.2058</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0649</v>
+        <v>0.0391</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1609</v>
+        <v>-0.2478</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2259</v>
+        <v>0.2869</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7617</v>
+        <v>-1.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3002</v>
+        <v>-2.3149</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.307700000000001</v>
+        <v>-8.1419</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.0325</v>
+        <v>-6.8416</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2752</v>
+        <v>-1.3003</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.377</v>
+        <v>-7.1507</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6976</v>
+        <v>-1.6163</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.6794</v>
+        <v>-5.5343</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.8644</v>
+        <v>-5.5951</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6947</v>
+        <v>-1.5899</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.1697</v>
+        <v>-4.0052</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5126</v>
+        <v>-1.5556</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0029</v>
+        <v>-0.0264</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5097</v>
+        <v>-1.5291</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0228</v>
+        <v>-0.0665</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0143</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0326</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3694</v>
+        <v>-1.3838</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3694</v>
+        <v>-1.3838</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.7905</v>
+        <v>-24.7351</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.2049</v>
+        <v>-19.6954</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.5854</v>
+        <v>-5.039700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-27.7647</v>
+        <v>-27.2689</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.596500000000001</v>
+        <v>-7.4964</v>
       </c>
       <c r="I14" t="n">
-        <v>-20.1684</v>
+        <v>-19.7722</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.2475</v>
+        <v>-11.6688</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.8157</v>
+        <v>-4.998100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.4318</v>
+        <v>-6.6706</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.5174</v>
+        <v>-15.6001</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7808</v>
+        <v>-2.4982</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.7366</v>
+        <v>-13.1018</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3075</v>
+        <v>2.295</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.8453</v>
+        <v>-13.7699</v>
       </c>
       <c r="R14" t="n">
-        <v>16.1529</v>
+        <v>16.065</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2359</v>
+        <v>1.7994</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7438</v>
+        <v>-1.9558</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9796</v>
+        <v>3.7554</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5692</v>
+        <v>-1.5606</v>
       </c>
       <c r="W14" t="n">
-        <v>7.631600000000001</v>
+        <v>7.699000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.2006</v>
+        <v>-9.259699999999999</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4366</v>
+        <v>7.5048</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3799</v>
+        <v>3.5186</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0567</v>
+        <v>3.9862</v>
       </c>
       <c r="G15" t="n">
-        <v>8.3512</v>
+        <v>8.387600000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8046</v>
+        <v>2.7863</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5466</v>
+        <v>5.6013</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2678</v>
+        <v>6.4799</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1374</v>
+        <v>2.1924</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1304</v>
+        <v>4.2874</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0834</v>
+        <v>1.9077</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6672</v>
+        <v>0.5939</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4162</v>
+        <v>1.3138</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2224</v>
+        <v>-0.1943</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5804</v>
+        <v>-0.6663</v>
       </c>
       <c r="U15" t="n">
-        <v>0.358</v>
+        <v>0.472</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5375</v>
+        <v>5.3909</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2952</v>
+        <v>2.225</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2424</v>
+        <v>3.1659</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9993</v>
+        <v>5.7986</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1377</v>
+        <v>2.0596</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8617</v>
+        <v>3.739</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8756</v>
+        <v>2.8913</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4724</v>
+        <v>1.4834</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4031</v>
+        <v>1.4079</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1238</v>
+        <v>2.9073</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6652</v>
+        <v>0.5762</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4585</v>
+        <v>2.3311</v>
       </c>
       <c r="P16" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6923</v>
+        <v>-0.6207</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5804</v>
+        <v>-0.6663</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.112</v>
+        <v>0.0456</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.879</v>
+        <v>4.8475</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1884</v>
+        <v>2.2081</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6906</v>
+        <v>2.6394</v>
       </c>
       <c r="G17" t="n">
-        <v>1.854</v>
+        <v>1.7832</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5502</v>
+        <v>1.5069</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3038</v>
+        <v>0.2763</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9514</v>
+        <v>1.0338</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0542</v>
+        <v>1.1012</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1028</v>
+        <v>-0.0674</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9026</v>
+        <v>0.7494</v>
       </c>
       <c r="N17" t="n">
-        <v>0.496</v>
+        <v>0.4057</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4066</v>
+        <v>0.3437</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S17" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2369</v>
+        <v>0.1578</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1504</v>
+        <v>-0.0378</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9385</v>
+        <v>2.9443</v>
       </c>
       <c r="W17" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7846</v>
+        <v>0.7803</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1877</v>
+        <v>4.1611</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0608</v>
+        <v>2.0531</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1268</v>
+        <v>2.108</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6745</v>
+        <v>3.5393</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1582</v>
+        <v>-0.2063</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8327</v>
+        <v>3.7457</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4681</v>
+        <v>2.5136</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4859</v>
+        <v>-0.4504</v>
       </c>
       <c r="L18" t="n">
-        <v>2.954</v>
+        <v>2.964</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2064</v>
+        <v>1.0257</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3277</v>
+        <v>0.244</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8787</v>
+        <v>0.7816</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.2295</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.1475</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="S18" t="n">
         <v>-0.2308</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.1538</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.333</v>
-      </c>
       <c r="T18" t="n">
-        <v>-0.3304</v>
+        <v>-0.3951</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0026</v>
+        <v>0.1643</v>
       </c>
       <c r="V18" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W18" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5719</v>
+        <v>3.531</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1182</v>
+        <v>1.1271</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4537</v>
+        <v>2.4039</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3685</v>
+        <v>2.2958</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2355</v>
+        <v>1.2447</v>
       </c>
       <c r="I19" t="n">
-        <v>1.133</v>
+        <v>1.0511</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7899</v>
+        <v>0.8731</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5683</v>
+        <v>0.6508</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2215</v>
+        <v>0.2223</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5786</v>
+        <v>1.4226</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6672</v>
+        <v>0.5939</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9114</v>
+        <v>0.8288</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0349</v>
+        <v>0.0091</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5179</v>
+        <v>-0.5985</v>
       </c>
       <c r="U19" t="n">
-        <v>0.483</v>
+        <v>0.6076</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W19" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.113</v>
+        <v>3.1802</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3213</v>
+        <v>0.4397</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7917</v>
+        <v>2.7405</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5336</v>
+        <v>0.5844</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0081</v>
+        <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5417</v>
+        <v>0.5221</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9094</v>
+        <v>-0.7237</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8435</v>
+        <v>-0.6933</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0659</v>
+        <v>-0.0304</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4431</v>
+        <v>1.3081</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8354</v>
+        <v>0.7556</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6076</v>
+        <v>0.5525</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R20" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5024</v>
+        <v>0.5138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2234</v>
+        <v>-0.3156</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7258</v>
+        <v>0.8293</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6155</v>
+        <v>1.623</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8387</v>
+        <v>2.8559</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3133</v>
+        <v>1.2572</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2983</v>
+        <v>0.2899</v>
       </c>
       <c r="F21" t="n">
-        <v>1.015</v>
+        <v>0.9673</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7574</v>
+        <v>2.6408</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2588</v>
+        <v>-0.2998</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0161</v>
+        <v>2.9406</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0557</v>
+        <v>2.1002</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4182</v>
+        <v>-0.3822</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4739</v>
+        <v>2.4824</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7016</v>
+        <v>0.5406</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1594</v>
+        <v>0.0824</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5422</v>
+        <v>0.4583</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2825</v>
+        <v>-0.223</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5191</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2366</v>
+        <v>0.3612</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9308</v>
+        <v>-0.9312</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8125</v>
+        <v>-0.7584</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0022</v>
+        <v>-1.8846</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1898</v>
+        <v>1.1261</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5321</v>
+        <v>-0.4996</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7015</v>
+        <v>-1.6516</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1694</v>
+        <v>1.152</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2664</v>
+        <v>-1.0873</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1975</v>
+        <v>-2.0573</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9311</v>
+        <v>0.97</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7343</v>
+        <v>0.5877</v>
       </c>
       <c r="N22" t="n">
-        <v>0.496</v>
+        <v>0.4057</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2384</v>
+        <v>0.182</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2957</v>
+        <v>-0.2686</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.036</v>
+        <v>-0.1121</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2597</v>
+        <v>-0.1565</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2461</v>
+        <v>0.2393</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4386</v>
+        <v>-0.4526</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8647</v>
+        <v>-0.8384</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0746</v>
+        <v>-3.0118</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2099</v>
+        <v>2.1734</v>
       </c>
       <c r="G23" t="n">
-        <v>3.7334</v>
+        <v>3.6998</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1087</v>
+        <v>2.0696</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6247</v>
+        <v>1.6302</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7855</v>
+        <v>1.9067</v>
       </c>
       <c r="K23" t="n">
-        <v>1.105</v>
+        <v>1.1524</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6805</v>
+        <v>0.7543</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9479</v>
+        <v>1.7931</v>
       </c>
       <c r="N23" t="n">
-        <v>1.0037</v>
+        <v>0.9172</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9442</v>
+        <v>0.8759</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9998</v>
+        <v>-2.9834</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.6151</v>
+        <v>-4.5899</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1634</v>
+        <v>0.2191</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2451</v>
+        <v>-0.3286</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4085</v>
+        <v>0.5477</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7617</v>
+        <v>-1.7739</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7617</v>
+        <v>-1.7739</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,64 +2392,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1052</v>
+        <v>-2.0542</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0766</v>
+        <v>-3.0075</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9715</v>
+        <v>0.9533</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.975</v>
+        <v>-0.9611</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1136</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.8858</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5007</v>
+        <v>-0.3875</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6115</v>
+        <v>-0.4986</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1108</v>
+        <v>0.1112</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4743</v>
+        <v>-0.5736</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4979</v>
+        <v>0.4234</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9722</v>
+        <v>-0.9969</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5383</v>
+        <v>-2.5244</v>
       </c>
       <c r="R24" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3389</v>
+        <v>0.3625</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1838</v>
+        <v>-0.2464</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6089</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.2566</v>
+        <v>26.22170000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>3.5087</v>
+        <v>3.957600000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>22.7481</v>
+        <v>22.264</v>
       </c>
       <c r="G25" t="n">
-        <v>27.7648</v>
+        <v>27.2688</v>
       </c>
       <c r="H25" t="n">
-        <v>7.596500000000001</v>
+        <v>7.4964</v>
       </c>
       <c r="I25" t="n">
-        <v>20.1683</v>
+        <v>19.7725</v>
       </c>
       <c r="J25" t="n">
-        <v>14.5175</v>
+        <v>15.6001</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7807</v>
+        <v>2.4984</v>
       </c>
       <c r="L25" t="n">
-        <v>12.7366</v>
+        <v>13.1017</v>
       </c>
       <c r="M25" t="n">
-        <v>13.2474</v>
+        <v>11.6686</v>
       </c>
       <c r="N25" t="n">
-        <v>5.8157</v>
+        <v>4.998</v>
       </c>
       <c r="O25" t="n">
-        <v>7.4316</v>
+        <v>6.6708</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.3078</v>
+        <v>-2.2949</v>
       </c>
       <c r="Q25" t="n">
-        <v>-16.1528</v>
+        <v>-16.0648</v>
       </c>
       <c r="R25" t="n">
-        <v>13.8453</v>
+        <v>13.77</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7696000000000001</v>
+        <v>-0.3129000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.9796</v>
+        <v>-3.7553</v>
       </c>
       <c r="U25" t="n">
-        <v>2.2099</v>
+        <v>3.4423</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5691</v>
+        <v>1.5605</v>
       </c>
       <c r="W25" t="n">
-        <v>8.123799999999999</v>
+        <v>8.1776</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.554600000000001</v>
+        <v>-6.617000000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105350_W1.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105350_W1.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5196</v>
+        <v>2.5604</v>
       </c>
       <c r="E2" t="n">
-        <v>3.708</v>
+        <v>3.6009</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1883</v>
+        <v>-1.0405</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8465</v>
+        <v>2.8335</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3106</v>
+        <v>1.3089</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536</v>
+        <v>1.5246</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7523</v>
+        <v>3.6874</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3811</v>
+        <v>1.3448</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3712</v>
+        <v>2.3426</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9058</v>
+        <v>-0.8539</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0359</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8353</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6076</v>
+        <v>0.6211</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0443</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.652</v>
+        <v>0.7077</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1835</v>
+        <v>1.1717</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4984</v>
+        <v>-0.6478</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6819</v>
+        <v>1.8195</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.142</v>
+        <v>-2.1213</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1182</v>
+        <v>0.1315</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2602</v>
+        <v>-2.2528</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4275</v>
+        <v>-1.4629</v>
       </c>
       <c r="K3" t="n">
-        <v>0.368</v>
+        <v>0.3379</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.7955</v>
+        <v>-1.8008</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7146</v>
+        <v>-0.6584</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2498</v>
+        <v>-0.2064</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4648</v>
+        <v>-0.4519</v>
       </c>
       <c r="P3" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1786</v>
+        <v>0.1433</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0743</v>
+        <v>-0.1493</v>
       </c>
       <c r="U3" t="n">
-        <v>0.253</v>
+        <v>0.2926</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3109</v>
+        <v>1.278</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X3" t="n">
-        <v>0.078</v>
+        <v>0.0796</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3237</v>
+        <v>0.3424</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1116</v>
+        <v>-0.0348</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2121</v>
+        <v>0.3772</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2814</v>
+        <v>-0.2689</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4427</v>
+        <v>0.4393</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7241</v>
+        <v>-0.7081</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9566</v>
+        <v>0.9126</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8454</v>
+        <v>0.8028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1112</v>
+        <v>0.1098</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.238</v>
+        <v>-1.1814</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4027</v>
+        <v>-0.3635</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8353</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R4" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6911</v>
+        <v>0.66</v>
       </c>
       <c r="T4" t="n">
-        <v>0.532</v>
+        <v>0.4565</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1591</v>
+        <v>0.2035</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.004</v>
+        <v>-0.9846</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.004</v>
+        <v>-0.9846</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4572</v>
+        <v>-0.4716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8383</v>
+        <v>0.6647</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2955</v>
+        <v>-1.1363</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8833</v>
+        <v>-3.8546</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5621</v>
+        <v>-0.5555</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.3212</v>
+        <v>-3.2991</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1457</v>
+        <v>-1.2001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0199</v>
+        <v>-0.0215</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1656</v>
+        <v>-1.1786</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7376</v>
+        <v>-2.6545</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.582</v>
+        <v>-0.534</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1556</v>
+        <v>-2.1205</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4264</v>
+        <v>-0.4471</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7211</v>
+        <v>-0.7955</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2947</v>
+        <v>0.3484</v>
       </c>
       <c r="V5" t="n">
-        <v>2.705</v>
+        <v>2.6603</v>
       </c>
       <c r="W5" t="n">
-        <v>2.705</v>
+        <v>2.6603</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6551</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7098</v>
+        <v>-0.7859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0547</v>
+        <v>0.1523</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.575</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7502</v>
+        <v>-0.7305</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1752</v>
+        <v>0.1767</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1133</v>
+        <v>-0.1224</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7081</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5928</v>
+        <v>0.5856</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4617</v>
+        <v>-0.4314</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0441</v>
+        <v>-0.0224</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4176</v>
+        <v>-0.409</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R6" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5568</v>
+        <v>0.5305</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4134</v>
+        <v>0.3661</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1434</v>
+        <v>0.1644</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7843</v>
+        <v>-1.7801</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7803</v>
+        <v>-0.7955</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.004</v>
+        <v>-0.9846</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3618</v>
+        <v>-1.3986</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7356</v>
+        <v>-3.003</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3738</v>
+        <v>1.6044</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.2407</v>
+        <v>-5.191</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.815</v>
+        <v>-1.7796</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.4257</v>
+        <v>-3.4114</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2088</v>
+        <v>-3.2506</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1977</v>
+        <v>-1.2277</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0111</v>
+        <v>-2.0229</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0319</v>
+        <v>-1.9404</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6173</v>
+        <v>-0.552</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4146</v>
+        <v>-1.3885</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R7" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0236</v>
+        <v>1.018</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0091</v>
+        <v>-0.1076</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0327</v>
+        <v>1.1256</v>
       </c>
       <c r="V7" t="n">
-        <v>3.0848</v>
+        <v>3.0084</v>
       </c>
       <c r="W7" t="n">
-        <v>3.0068</v>
+        <v>2.9289</v>
       </c>
       <c r="X7" t="n">
-        <v>0.078</v>
+        <v>0.0796</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6875</v>
+        <v>-2.717</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5662</v>
+        <v>-2.6295</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1213</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5881</v>
+        <v>-0.575</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5793</v>
+        <v>-0.5705</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,31 +1095,31 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5881</v>
+        <v>-0.575</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5793</v>
+        <v>-0.5705</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0655</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0339</v>
+        <v>-0.0362</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2712</v>
+        <v>-0.2897</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2373</v>
+        <v>0.2535</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.379</v>
+        <v>-3.3857</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9061</v>
+        <v>-4.1413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.527</v>
+        <v>0.7556</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3078</v>
+        <v>-3.2812</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9295</v>
+        <v>-0.901</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3782</v>
+        <v>-2.3801</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5257</v>
+        <v>-1.6074</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4475</v>
+        <v>-0.4972</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0782</v>
+        <v>-1.1102</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7821</v>
+        <v>-1.6738</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.482</v>
+        <v>-0.4039</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3</v>
+        <v>-1.2699</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1395</v>
+        <v>-0.1546</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7641</v>
+        <v>-0.8666</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6246</v>
+        <v>0.712</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1612</v>
+        <v>-0.1839</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="X9" t="n">
-        <v>0.078</v>
+        <v>0.0796</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4395</v>
+        <v>-3.4424</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0261</v>
+        <v>-1.1702</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4134</v>
+        <v>-2.2722</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4733</v>
+        <v>-0.4466</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8102</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3369</v>
+        <v>0.3382</v>
       </c>
       <c r="J10" t="n">
-        <v>0.947</v>
+        <v>0.9258</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7573</v>
+        <v>-0.7579</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7043</v>
+        <v>1.6837</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4203</v>
+        <v>-1.3725</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0529</v>
+        <v>-0.0269</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3675</v>
+        <v>-1.3455</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7367</v>
+        <v>-0.7618</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7602</v>
+        <v>-0.8205</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0235</v>
+        <v>0.0586</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W10" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6593</v>
+        <v>-3.6756</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7224</v>
+        <v>-3.8147</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0631</v>
+        <v>0.1391</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6863</v>
+        <v>-3.658</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1836</v>
+        <v>-1.173</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5027</v>
+        <v>-2.4851</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8157</v>
+        <v>-2.8221</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.31</v>
+        <v>-1.3165</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5057</v>
+        <v>-1.5056</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8359</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1264</v>
+        <v>0.1436</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9969</v>
+        <v>-0.9795</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R11" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1056</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09</v>
+        <v>0.043</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0156</v>
+        <v>0.0391</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9806</v>
+        <v>-4.9567</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3471</v>
+        <v>-2.4961</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6335</v>
+        <v>-2.4607</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7868</v>
+        <v>-2.7833</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6922</v>
+        <v>-1.7092</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0946</v>
+        <v>-1.0742</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4929</v>
+        <v>-1.5545</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.604</v>
+        <v>-1.6643</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1112</v>
+        <v>0.1098</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2939</v>
+        <v>-1.2289</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0881</v>
+        <v>-0.0449</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2058</v>
+        <v>-1.184</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0391</v>
+        <v>0.025</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2478</v>
+        <v>-0.3038</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2869</v>
+        <v>0.3288</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7739</v>
+        <v>-1.7305</v>
       </c>
       <c r="W12" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3149</v>
+        <v>-2.2625</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.1419</v>
+        <v>-8.0901</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.8416</v>
+        <v>-6.9319</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3003</v>
+        <v>-1.1582</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.1507</v>
+        <v>-7.1319</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6163</v>
+        <v>-1.623</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.5343</v>
+        <v>-5.5089</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.5951</v>
+        <v>-5.6114</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5899</v>
+        <v>-1.6095</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0052</v>
+        <v>-4.0019</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5556</v>
+        <v>-1.5205</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0264</v>
+        <v>-0.0135</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5291</v>
+        <v>-1.5071</v>
       </c>
       <c r="P13" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0665</v>
+        <v>-0.0934</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1506</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0326</v>
+        <v>0.0572</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3838</v>
+        <v>-1.3327</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3838</v>
+        <v>-1.3327</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.7351</v>
+        <v>-24.6968</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.6954</v>
+        <v>-21.3896</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.039700000000001</v>
+        <v>-3.307300000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-27.2689</v>
+        <v>-27.0322</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.4964</v>
+        <v>-7.381400000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-19.7722</v>
+        <v>-19.6507</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.6688</v>
+        <v>-12.1056</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.998100000000001</v>
+        <v>-5.3172</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.6706</v>
+        <v>-6.788500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.6001</v>
+        <v>-14.9266</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4982</v>
+        <v>-2.0643</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.1018</v>
+        <v>-12.8624</v>
       </c>
       <c r="P14" t="n">
-        <v>2.295</v>
+        <v>2.339799999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.7699</v>
+        <v>-14.0384</v>
       </c>
       <c r="R14" t="n">
-        <v>16.065</v>
+        <v>16.378</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7994</v>
+        <v>1.5869</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9558</v>
+        <v>-2.704499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7554</v>
+        <v>4.2914</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5606</v>
+        <v>-1.5911</v>
       </c>
       <c r="W14" t="n">
-        <v>7.699000000000001</v>
+        <v>7.459199999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.259699999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5048</v>
+        <v>7.3739</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5186</v>
+        <v>3.2429</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9862</v>
+        <v>4.131</v>
       </c>
       <c r="G15" t="n">
-        <v>8.387600000000001</v>
+        <v>8.2582</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7863</v>
+        <v>2.7336</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6013</v>
+        <v>5.5246</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4799</v>
+        <v>6.314</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1924</v>
+        <v>2.1144</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2874</v>
+        <v>4.1996</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9077</v>
+        <v>1.9442</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5939</v>
+        <v>0.6192</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3138</v>
+        <v>1.325</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1943</v>
+        <v>-0.1824</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6663</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.472</v>
+        <v>0.549</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3909</v>
+        <v>5.4653</v>
       </c>
       <c r="E16" t="n">
-        <v>2.225</v>
+        <v>2.104</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1659</v>
+        <v>3.3613</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7986</v>
+        <v>5.7828</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0596</v>
+        <v>2.0547</v>
       </c>
       <c r="I16" t="n">
-        <v>3.739</v>
+        <v>3.7281</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8913</v>
+        <v>2.8353</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4834</v>
+        <v>1.4444</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4079</v>
+        <v>1.3909</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9073</v>
+        <v>2.9474</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5762</v>
+        <v>0.6102</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3311</v>
+        <v>2.3372</v>
       </c>
       <c r="P16" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6207</v>
+        <v>-0.5931</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6663</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0456</v>
+        <v>0.1382</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.8475</v>
+        <v>4.842</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2081</v>
+        <v>2.05</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6394</v>
+        <v>2.7921</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7832</v>
+        <v>1.7762</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5069</v>
+        <v>1.496</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2763</v>
+        <v>0.2801</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0338</v>
+        <v>0.9762</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1012</v>
+        <v>1.0518</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0674</v>
+        <v>-0.0756</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7494</v>
+        <v>0.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4057</v>
+        <v>0.4442</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3437</v>
+        <v>0.3558</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S17" t="n">
-        <v>0.12</v>
+        <v>0.1421</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1578</v>
+        <v>0.1154</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0378</v>
+        <v>0.0267</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9443</v>
+        <v>2.9237</v>
       </c>
       <c r="W17" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7803</v>
+        <v>0.7955</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1611</v>
+        <v>4.2028</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0531</v>
+        <v>1.9218</v>
       </c>
       <c r="F18" t="n">
-        <v>2.108</v>
+        <v>2.281</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5393</v>
+        <v>3.5493</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2063</v>
+        <v>-0.1764</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7457</v>
+        <v>3.7257</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5136</v>
+        <v>2.4692</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4504</v>
+        <v>-0.459</v>
       </c>
       <c r="L18" t="n">
-        <v>2.964</v>
+        <v>2.9282</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0257</v>
+        <v>1.0801</v>
       </c>
       <c r="N18" t="n">
-        <v>0.244</v>
+        <v>0.2827</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7816</v>
+        <v>0.7974</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R18" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2308</v>
+        <v>-0.1766</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3951</v>
+        <v>-0.4416</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1643</v>
+        <v>0.265</v>
       </c>
       <c r="V18" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W18" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.531</v>
+        <v>3.5765</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1271</v>
+        <v>0.9836</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4039</v>
+        <v>2.5929</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2958</v>
+        <v>2.272</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2447</v>
+        <v>1.212</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0511</v>
+        <v>1.06</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8731</v>
+        <v>0.8124</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6508</v>
+        <v>0.5928</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2223</v>
+        <v>0.2196</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4226</v>
+        <v>1.4596</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5939</v>
+        <v>0.6192</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8288</v>
+        <v>0.8404</v>
       </c>
       <c r="P19" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0091</v>
+        <v>0.0349</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5985</v>
+        <v>-0.6589</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6076</v>
+        <v>0.6939</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W19" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1802</v>
+        <v>3.1412</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4397</v>
+        <v>0.2185</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7405</v>
+        <v>2.9227</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5844</v>
+        <v>0.545</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0623</v>
+        <v>0.0238</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5221</v>
+        <v>0.5212</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7237</v>
+        <v>-0.796</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6933</v>
+        <v>-0.757</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0304</v>
+        <v>-0.039</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3081</v>
+        <v>1.341</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7556</v>
+        <v>0.7808</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5525</v>
+        <v>0.5603</v>
       </c>
       <c r="P20" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R20" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5138</v>
+        <v>0.532</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3156</v>
+        <v>-0.3762</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8293</v>
+        <v>0.9083</v>
       </c>
       <c r="V20" t="n">
-        <v>1.623</v>
+        <v>1.5962</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8559</v>
+        <v>2.7946</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2572</v>
+        <v>1.298</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2899</v>
+        <v>0.155</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9673</v>
+        <v>1.143</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6408</v>
+        <v>2.6553</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2998</v>
+        <v>-0.2715</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9406</v>
+        <v>2.9267</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1002</v>
+        <v>2.0598</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3822</v>
+        <v>-0.3926</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4824</v>
+        <v>2.4524</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5406</v>
+        <v>0.5955</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0824</v>
+        <v>0.1211</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4583</v>
+        <v>0.4744</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.223</v>
+        <v>-0.1934</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.6352</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3612</v>
+        <v>0.4418</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9312</v>
+        <v>-0.9298</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7584</v>
+        <v>-0.727</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8846</v>
+        <v>-2.0324</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1261</v>
+        <v>1.3054</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4996</v>
+        <v>-0.4975</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6516</v>
+        <v>-1.641</v>
       </c>
       <c r="I22" t="n">
-        <v>1.152</v>
+        <v>1.1435</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0873</v>
+        <v>-1.1359</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0573</v>
+        <v>-2.0852</v>
       </c>
       <c r="L22" t="n">
-        <v>0.97</v>
+        <v>0.9492</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5877</v>
+        <v>0.6384</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4057</v>
+        <v>0.4442</v>
       </c>
       <c r="O22" t="n">
-        <v>0.182</v>
+        <v>0.1942</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2686</v>
+        <v>-0.259</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1121</v>
+        <v>-0.1589</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1565</v>
+        <v>-0.1</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2393</v>
+        <v>0.2634</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4526</v>
+        <v>-0.4029</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8384</v>
+        <v>-0.8613</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0118</v>
+        <v>-3.2352</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1734</v>
+        <v>2.3739</v>
       </c>
       <c r="G23" t="n">
-        <v>3.6998</v>
+        <v>3.6544</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0696</v>
+        <v>2.0439</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6302</v>
+        <v>1.6105</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9067</v>
+        <v>1.8288</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1524</v>
+        <v>1.1016</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7543</v>
+        <v>0.7272</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7931</v>
+        <v>1.8256</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9172</v>
+        <v>0.9423</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8759</v>
+        <v>0.8833</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9834</v>
+        <v>-3.0416</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5899</v>
+        <v>-4.6794</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2191</v>
+        <v>0.2564</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3286</v>
+        <v>-0.3846</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5477</v>
+        <v>0.641</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7739</v>
+        <v>-1.7305</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7739</v>
+        <v>-1.7305</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,64 +2392,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0542</v>
+        <v>-2.0825</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0075</v>
+        <v>-3.165</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9533</v>
+        <v>1.0825</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9611</v>
+        <v>-0.9635</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8858</v>
+        <v>-0.8697</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3875</v>
+        <v>-0.4372</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4986</v>
+        <v>-0.547</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1112</v>
+        <v>0.1098</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5736</v>
+        <v>-0.5263</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4234</v>
+        <v>0.4532</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9969</v>
+        <v>-0.9795</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R24" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3625</v>
+        <v>0.3844</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2464</v>
+        <v>-0.2884</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6089</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.22170000000001</v>
+        <v>26.2289</v>
       </c>
       <c r="E25" t="n">
-        <v>3.957600000000001</v>
+        <v>2.2432</v>
       </c>
       <c r="F25" t="n">
-        <v>22.264</v>
+        <v>23.9858</v>
       </c>
       <c r="G25" t="n">
-        <v>27.2688</v>
+        <v>27.0322</v>
       </c>
       <c r="H25" t="n">
-        <v>7.4964</v>
+        <v>7.381299999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>19.7725</v>
+        <v>19.6507</v>
       </c>
       <c r="J25" t="n">
-        <v>15.6001</v>
+        <v>14.9266</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4984</v>
+        <v>2.0642</v>
       </c>
       <c r="L25" t="n">
-        <v>13.1017</v>
+        <v>12.8623</v>
       </c>
       <c r="M25" t="n">
-        <v>11.6686</v>
+        <v>12.1055</v>
       </c>
       <c r="N25" t="n">
-        <v>4.998</v>
+        <v>5.3171</v>
       </c>
       <c r="O25" t="n">
-        <v>6.6708</v>
+        <v>6.788500000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2949</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q25" t="n">
-        <v>-16.0648</v>
+        <v>-16.378</v>
       </c>
       <c r="R25" t="n">
-        <v>13.77</v>
+        <v>14.0385</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3129000000000001</v>
+        <v>-0.05469999999999986</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.7553</v>
+        <v>-4.2912</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4423</v>
+        <v>4.236800000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5605</v>
+        <v>1.5909</v>
       </c>
       <c r="W25" t="n">
-        <v>8.1776</v>
+        <v>7.986</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.617000000000001</v>
+        <v>-6.395</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105350_W1.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105350_W1.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5604</v>
+        <v>2.5623</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6009</v>
+        <v>3.6672</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0405</v>
+        <v>-1.1049</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8335</v>
+        <v>2.8591</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3089</v>
+        <v>1.323</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5246</v>
+        <v>1.5361</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6874</v>
+        <v>3.715</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3448</v>
+        <v>1.3602</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3426</v>
+        <v>2.3547</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8539</v>
+        <v>-0.8559</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0359</v>
+        <v>-0.0372</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.8186</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6211</v>
+        <v>0.6146</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0477</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7077</v>
+        <v>0.6623</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1717</v>
+        <v>1.1847</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6478</v>
+        <v>-0.5806</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8195</v>
+        <v>1.7653</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1213</v>
+        <v>-2.1418</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1315</v>
+        <v>0.1325</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2528</v>
+        <v>-2.2743</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4629</v>
+        <v>-1.4813</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3379</v>
+        <v>0.3423</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.8008</v>
+        <v>-1.8236</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6584</v>
+        <v>-0.6605</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2064</v>
+        <v>-0.2098</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4519</v>
+        <v>-0.4507</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1433</v>
+        <v>0.1779</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1493</v>
+        <v>-0.0803</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2926</v>
+        <v>0.2582</v>
       </c>
       <c r="V3" t="n">
-        <v>1.278</v>
+        <v>1.292</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0796</v>
+        <v>0.0789</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3424</v>
+        <v>0.3671</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0348</v>
+        <v>0.0625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3772</v>
+        <v>0.3046</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2689</v>
+        <v>-0.2641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4393</v>
+        <v>0.4441</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7081</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9126</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8028</v>
+        <v>0.8125</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1098</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1814</v>
+        <v>-1.1871</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3635</v>
+        <v>-0.3684</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.8186</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="S4" t="n">
-        <v>0.66</v>
+        <v>0.6957</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4565</v>
+        <v>0.532</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2035</v>
+        <v>0.1638</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9846</v>
+        <v>-0.9928</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9846</v>
+        <v>-0.9928</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4716</v>
+        <v>-0.4793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6647</v>
+        <v>0.7271</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1363</v>
+        <v>-1.2064</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8546</v>
+        <v>-3.8869</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5555</v>
+        <v>-0.5616</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.2991</v>
+        <v>-3.3252</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2001</v>
+        <v>-1.2188</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0206</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1786</v>
+        <v>-1.1982</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6545</v>
+        <v>-2.6681</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.534</v>
+        <v>-0.541</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1205</v>
+        <v>-2.1271</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4471</v>
+        <v>-0.432</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7955</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3484</v>
+        <v>0.3013</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6603</v>
+        <v>2.6793</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6603</v>
+        <v>2.6793</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.6206</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7859</v>
+        <v>-0.7339</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1523</v>
+        <v>0.1134</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5595</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7305</v>
+        <v>-0.7389</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1767</v>
+        <v>0.1794</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1224</v>
+        <v>-0.1269</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7081</v>
+        <v>-0.7156</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5856</v>
+        <v>0.5887</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4314</v>
+        <v>-0.4326</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0224</v>
+        <v>-0.0233</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.409</v>
+        <v>-0.4093</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5305</v>
+        <v>0.5604</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3661</v>
+        <v>0.4141</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1644</v>
+        <v>0.1463</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7801</v>
+        <v>-1.7819</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7955</v>
+        <v>-0.789</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9846</v>
+        <v>-0.9928</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3986</v>
+        <v>-1.4001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.003</v>
+        <v>-2.8983</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6044</v>
+        <v>1.4982</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.191</v>
+        <v>-5.2422</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7796</v>
+        <v>-1.7997</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.4114</v>
+        <v>-3.4425</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2506</v>
+        <v>-3.2913</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2277</v>
+        <v>-1.24</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0229</v>
+        <v>-2.0513</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9404</v>
+        <v>-1.9508</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.552</v>
+        <v>-0.5596</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3885</v>
+        <v>-1.3912</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="S7" t="n">
-        <v>1.018</v>
+        <v>1.0333</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1076</v>
+        <v>-0.0161</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1256</v>
+        <v>1.0494</v>
       </c>
       <c r="V7" t="n">
-        <v>3.0084</v>
+        <v>3.0409</v>
       </c>
       <c r="W7" t="n">
-        <v>2.9289</v>
+        <v>2.962</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0796</v>
+        <v>0.0789</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.717</v>
+        <v>-2.7003</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6295</v>
+        <v>-2.5959</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.1044</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.575</v>
+        <v>-0.5772</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5705</v>
+        <v>-0.5726</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,31 +1095,31 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.575</v>
+        <v>-0.5772</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5705</v>
+        <v>-0.5726</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1057</v>
+        <v>-2.0886</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R8" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0362</v>
+        <v>-0.0344</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2897</v>
+        <v>-0.2752</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2535</v>
+        <v>0.2408</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3857</v>
+        <v>-3.4034</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1413</v>
+        <v>-4.064</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7556</v>
+        <v>0.6606</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2812</v>
+        <v>-3.3192</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.901</v>
+        <v>-0.9115</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3801</v>
+        <v>-2.4077</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6074</v>
+        <v>-1.6396</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4972</v>
+        <v>-0.5011</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1102</v>
+        <v>-1.1384</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6738</v>
+        <v>-1.6796</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4039</v>
+        <v>-0.4103</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2699</v>
+        <v>-1.2693</v>
       </c>
       <c r="P9" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1546</v>
+        <v>-0.142</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8666</v>
+        <v>-0.7788</v>
       </c>
       <c r="U9" t="n">
-        <v>0.712</v>
+        <v>0.6369</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1839</v>
+        <v>-0.1743</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2634</v>
+        <v>-0.2532</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0796</v>
+        <v>0.0789</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4424</v>
+        <v>-3.4291</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1702</v>
+        <v>-1.0944</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2722</v>
+        <v>-2.3347</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4466</v>
+        <v>-0.4513</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3382</v>
+        <v>0.3427</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9258</v>
+        <v>0.9265</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7579</v>
+        <v>-0.766</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6837</v>
+        <v>1.6925</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3725</v>
+        <v>-1.3777</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0269</v>
+        <v>-0.0279</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3455</v>
+        <v>-1.3498</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7618</v>
+        <v>-0.7458</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8205</v>
+        <v>-0.7719</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0586</v>
+        <v>0.0262</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6756</v>
+        <v>-3.6758</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8147</v>
+        <v>-3.7843</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1391</v>
+        <v>0.1085</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.658</v>
+        <v>-3.6901</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.173</v>
+        <v>-1.1858</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4851</v>
+        <v>-2.5043</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8221</v>
+        <v>-2.8528</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3165</v>
+        <v>-1.3305</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5056</v>
+        <v>-1.5224</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8359</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1436</v>
+        <v>0.1447</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9795</v>
+        <v>-0.9819</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="T11" t="n">
-        <v>0.043</v>
+        <v>0.0876</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0391</v>
+        <v>0.0174</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9567</v>
+        <v>-4.9777</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4961</v>
+        <v>-2.4487</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4607</v>
+        <v>-2.529</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7833</v>
+        <v>-2.8032</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7092</v>
+        <v>-1.727</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0742</v>
+        <v>-1.0762</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5545</v>
+        <v>-1.5701</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.6643</v>
+        <v>-1.6805</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1098</v>
+        <v>0.1104</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2289</v>
+        <v>-1.2331</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0449</v>
+        <v>-0.0465</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.184</v>
+        <v>-1.1865</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S12" t="n">
-        <v>0.025</v>
+        <v>0.0385</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3038</v>
+        <v>-0.2541</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3288</v>
+        <v>0.2926</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7305</v>
+        <v>-1.7489</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2625</v>
+        <v>-2.2848</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.0901</v>
+        <v>-8.1577</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9319</v>
+        <v>-6.9354</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1582</v>
+        <v>-1.2223</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.1319</v>
+        <v>-7.1984</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.623</v>
+        <v>-1.6402</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.5089</v>
+        <v>-5.5582</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.6114</v>
+        <v>-5.6713</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6095</v>
+        <v>-1.6263</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0019</v>
+        <v>-4.0451</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5205</v>
+        <v>-1.5271</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0135</v>
+        <v>-0.014</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5071</v>
+        <v>-1.5131</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0934</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1506</v>
+        <v>-0.1037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0572</v>
+        <v>0.0346</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3327</v>
+        <v>-1.3544</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3327</v>
+        <v>-1.3544</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.6968</v>
+        <v>-24.7299</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.3896</v>
+        <v>-20.6787</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.307300000000001</v>
+        <v>-4.0511</v>
       </c>
       <c r="G14" t="n">
-        <v>-27.0322</v>
+        <v>-27.2748</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.381400000000001</v>
+        <v>-7.463700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-19.6507</v>
+        <v>-19.811</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.1056</v>
+        <v>-12.2877</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.3172</v>
+        <v>-5.365600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.788500000000001</v>
+        <v>-6.9223</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.9266</v>
+        <v>-14.9869</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0643</v>
+        <v>-2.098</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.8624</v>
+        <v>-12.8887</v>
       </c>
       <c r="P14" t="n">
-        <v>2.339799999999999</v>
+        <v>2.320800000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.0384</v>
+        <v>-13.9244</v>
       </c>
       <c r="R14" t="n">
-        <v>16.378</v>
+        <v>16.245</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5869</v>
+        <v>1.8022</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.704499999999999</v>
+        <v>-2.0275</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2914</v>
+        <v>3.829800000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5911</v>
+        <v>-1.5781</v>
       </c>
       <c r="W14" t="n">
-        <v>7.459199999999999</v>
+        <v>7.561</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.139100000000001</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3739</v>
+        <v>7.4215</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2429</v>
+        <v>3.3445</v>
       </c>
       <c r="F15" t="n">
-        <v>4.131</v>
+        <v>4.0771</v>
       </c>
       <c r="G15" t="n">
-        <v>8.2582</v>
+        <v>8.3131</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7336</v>
+        <v>2.7643</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5246</v>
+        <v>5.5488</v>
       </c>
       <c r="J15" t="n">
-        <v>6.314</v>
+        <v>6.3426</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1144</v>
+        <v>2.1392</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1996</v>
+        <v>4.2035</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9442</v>
+        <v>1.9705</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6192</v>
+        <v>0.6252</v>
       </c>
       <c r="O15" t="n">
-        <v>1.325</v>
+        <v>1.3453</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1824</v>
+        <v>-0.1954</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.6774</v>
       </c>
       <c r="U15" t="n">
-        <v>0.549</v>
+        <v>0.4821</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4653</v>
+        <v>5.4654</v>
       </c>
       <c r="E16" t="n">
-        <v>2.104</v>
+        <v>2.1817</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3613</v>
+        <v>3.2838</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7828</v>
+        <v>5.8413</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0547</v>
+        <v>2.0768</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7281</v>
+        <v>3.7645</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8353</v>
+        <v>2.8591</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4444</v>
+        <v>1.461</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3909</v>
+        <v>1.3981</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9474</v>
+        <v>2.9822</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6102</v>
+        <v>0.6159</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3372</v>
+        <v>2.3663</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5931</v>
+        <v>-0.6249</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.6774</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1382</v>
+        <v>0.0526</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.842</v>
+        <v>4.8527</v>
       </c>
       <c r="E17" t="n">
-        <v>2.05</v>
+        <v>2.1234</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7921</v>
+        <v>2.7293</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7762</v>
+        <v>1.7975</v>
       </c>
       <c r="H17" t="n">
-        <v>1.496</v>
+        <v>1.5124</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2801</v>
+        <v>0.2852</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9762</v>
+        <v>0.9839</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0518</v>
+        <v>1.0644</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0756</v>
+        <v>-0.0805</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8</v>
+        <v>0.8136</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4442</v>
+        <v>0.4479</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3558</v>
+        <v>0.3657</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1421</v>
+        <v>0.1227</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1154</v>
+        <v>0.1564</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0267</v>
+        <v>-0.0337</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9237</v>
+        <v>2.9325</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7955</v>
+        <v>0.789</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2028</v>
+        <v>4.1888</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9218</v>
+        <v>1.9888</v>
       </c>
       <c r="F18" t="n">
-        <v>2.281</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5493</v>
+        <v>3.5785</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1764</v>
+        <v>-0.1791</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7257</v>
+        <v>3.7576</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4692</v>
+        <v>2.4797</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.459</v>
+        <v>-0.4637</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9282</v>
+        <v>2.9434</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0801</v>
+        <v>1.0988</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2827</v>
+        <v>0.2847</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7974</v>
+        <v>0.8141</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1766</v>
+        <v>-0.2293</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4416</v>
+        <v>-0.4022</v>
       </c>
       <c r="U18" t="n">
-        <v>0.265</v>
+        <v>0.173</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5765</v>
+        <v>3.5643</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9836</v>
+        <v>1.0525</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5929</v>
+        <v>2.5118</v>
       </c>
       <c r="G19" t="n">
-        <v>2.272</v>
+        <v>2.3021</v>
       </c>
       <c r="H19" t="n">
-        <v>1.212</v>
+        <v>1.2259</v>
       </c>
       <c r="I19" t="n">
-        <v>1.06</v>
+        <v>1.0763</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8124</v>
+        <v>0.8215</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5928</v>
+        <v>0.6007</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2196</v>
+        <v>0.2208</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4596</v>
+        <v>1.4807</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6192</v>
+        <v>0.6252</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8404</v>
+        <v>0.8555</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0349</v>
+        <v>0.011</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6589</v>
+        <v>-0.6086</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6939</v>
+        <v>0.6197</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1412</v>
+        <v>3.1435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2185</v>
+        <v>0.2982</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9227</v>
+        <v>2.8453</v>
       </c>
       <c r="G20" t="n">
-        <v>0.545</v>
+        <v>0.5517</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0238</v>
+        <v>0.0251</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5212</v>
+        <v>0.5266</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.796</v>
+        <v>-0.8071</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.757</v>
+        <v>-0.7633</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.039</v>
+        <v>-0.0437</v>
       </c>
       <c r="M20" t="n">
-        <v>1.341</v>
+        <v>1.3588</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7808</v>
+        <v>0.7884</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5603</v>
+        <v>0.5703</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S20" t="n">
-        <v>0.532</v>
+        <v>0.5201</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3762</v>
+        <v>-0.3229</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9083</v>
+        <v>0.843</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5962</v>
+        <v>1.6076</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7946</v>
+        <v>2.8206</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.298</v>
+        <v>1.292</v>
       </c>
       <c r="E21" t="n">
-        <v>0.155</v>
+        <v>0.224</v>
       </c>
       <c r="F21" t="n">
-        <v>1.143</v>
+        <v>1.068</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6553</v>
+        <v>2.6775</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2715</v>
+        <v>-0.2752</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9267</v>
+        <v>2.9527</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0598</v>
+        <v>2.0686</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3926</v>
+        <v>-0.3965</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4524</v>
+        <v>2.4651</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5955</v>
+        <v>0.609</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1211</v>
+        <v>0.1214</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4744</v>
+        <v>0.4876</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1934</v>
+        <v>-0.2231</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6352</v>
+        <v>-0.5935</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4418</v>
+        <v>0.3704</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9298</v>
+        <v>-0.9304</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.727</v>
+        <v>-0.7562</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0324</v>
+        <v>-1.9888</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3054</v>
+        <v>1.2326</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4975</v>
+        <v>-0.5067</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.641</v>
+        <v>-1.6588</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1435</v>
+        <v>1.1521</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1571</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0852</v>
+        <v>-2.1068</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9492</v>
+        <v>0.9497</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6384</v>
+        <v>0.6503</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4442</v>
+        <v>0.4479</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1942</v>
+        <v>0.2024</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.259</v>
+        <v>-0.2706</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1589</v>
+        <v>-0.1165</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1</v>
+        <v>-0.1541</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2634</v>
+        <v>0.2532</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4029</v>
+        <v>-0.424</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8613</v>
+        <v>-0.8566</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2352</v>
+        <v>-3.1404</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3739</v>
+        <v>2.2838</v>
       </c>
       <c r="G23" t="n">
-        <v>3.6544</v>
+        <v>3.6854</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0439</v>
+        <v>2.0665</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6105</v>
+        <v>1.6189</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8288</v>
+        <v>1.8368</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1016</v>
+        <v>1.1148</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7272</v>
+        <v>0.722</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8256</v>
+        <v>1.8486</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9423</v>
+        <v>0.9517</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8833</v>
+        <v>0.8969</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.0416</v>
+        <v>-3.0169</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.6794</v>
+        <v>-4.6414</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2564</v>
+        <v>0.2238</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3846</v>
+        <v>-0.3357</v>
       </c>
       <c r="U23" t="n">
-        <v>0.641</v>
+        <v>0.5596</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7305</v>
+        <v>-1.7489</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7305</v>
+        <v>-1.7489</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,64 +2392,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0825</v>
+        <v>-2.0813</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.165</v>
+        <v>-3.1044</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0825</v>
+        <v>1.0231</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9635</v>
+        <v>-0.9658</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8697</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4372</v>
+        <v>-0.4411</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.547</v>
+        <v>-0.5515</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1098</v>
+        <v>0.1104</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5263</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4532</v>
+        <v>0.4572</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9795</v>
+        <v>-0.9819</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3844</v>
+        <v>0.3676</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2884</v>
+        <v>-0.2518</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.2289</v>
+        <v>26.2341</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2432</v>
+        <v>2.979500000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>23.9858</v>
+        <v>23.2548</v>
       </c>
       <c r="G25" t="n">
-        <v>27.0322</v>
+        <v>27.2746</v>
       </c>
       <c r="H25" t="n">
-        <v>7.381299999999999</v>
+        <v>7.4636</v>
       </c>
       <c r="I25" t="n">
-        <v>19.6507</v>
+        <v>19.8112</v>
       </c>
       <c r="J25" t="n">
-        <v>14.9266</v>
+        <v>14.9869</v>
       </c>
       <c r="K25" t="n">
-        <v>2.0642</v>
+        <v>2.0983</v>
       </c>
       <c r="L25" t="n">
-        <v>12.8623</v>
+        <v>12.8888</v>
       </c>
       <c r="M25" t="n">
-        <v>12.1055</v>
+        <v>12.2878</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3171</v>
+        <v>5.3655</v>
       </c>
       <c r="O25" t="n">
-        <v>6.788500000000001</v>
+        <v>6.9222</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.3398</v>
+        <v>-2.3208</v>
       </c>
       <c r="Q25" t="n">
-        <v>-16.378</v>
+        <v>-16.245</v>
       </c>
       <c r="R25" t="n">
-        <v>14.0385</v>
+        <v>13.9245</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.05469999999999986</v>
+        <v>-0.2981000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.2912</v>
+        <v>-3.8296</v>
       </c>
       <c r="U25" t="n">
-        <v>4.236800000000001</v>
+        <v>3.532</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5909</v>
+        <v>1.5781</v>
       </c>
       <c r="W25" t="n">
-        <v>7.986</v>
+        <v>8.067200000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.395</v>
+        <v>-6.4892</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
